--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -37356,7 +37356,7 @@
         <v>1071</v>
       </c>
       <c r="B794" t="n">
-        <v>2.25357142857143</v>
+        <v>2.25789473684211</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="1072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="1073">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -3236,6 +3236,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jul 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -37356,7 +37359,15 @@
         <v>1071</v>
       </c>
       <c r="B794" t="n">
-        <v>2.25789473684211</v>
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B795" t="n">
+        <v>2.27</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="1073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="1074">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -2659,6 +2659,9 @@
     <t xml:space="preserve">Jun 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Jul 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">UnempRate</t>
   </si>
   <si>
@@ -2668,6 +2671,9 @@
     <t xml:space="preserve">2026 Q2</t>
   </si>
   <si>
+    <t xml:space="preserve">2026 Q3</t>
+  </si>
+  <si>
     <t xml:space="preserve">M2growth</t>
   </si>
   <si>
@@ -3233,9 +3239,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jun 1968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jul 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Aug 2026</t>
@@ -18916,6 +18919,14 @@
         <v>21139.7</v>
       </c>
     </row>
+    <row r="608">
+      <c r="A608" t="s">
+        <v>879</v>
+      </c>
+      <c r="B608" t="n">
+        <v>21214.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -18933,7 +18944,7 @@
         <v>263</v>
       </c>
       <c r="B1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="2">
@@ -23782,6 +23793,14 @@
       </c>
       <c r="B607" t="n">
         <v>6.5</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="s">
+        <v>879</v>
+      </c>
+      <c r="B608" t="n">
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -23801,7 +23820,7 @@
         <v>263</v>
       </c>
       <c r="B1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="2">
@@ -25414,9 +25433,15 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B203"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>883</v>
+      </c>
+      <c r="B204"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25435,12 +25460,12 @@
         <v>263</v>
       </c>
       <c r="B1" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B2" t="n">
         <v>12.9667760753128</v>
@@ -25448,7 +25473,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B3" t="n">
         <v>15.0136942094219</v>
@@ -25456,7 +25481,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B4" t="n">
         <v>15.7173673795166</v>
@@ -25464,7 +25489,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B5" t="n">
         <v>15.0083394292738</v>
@@ -25472,7 +25497,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B6" t="n">
         <v>14.1631513522075</v>
@@ -25480,7 +25505,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B7" t="n">
         <v>14.3196627658395</v>
@@ -25488,7 +25513,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B8" t="n">
         <v>14.5659126107761</v>
@@ -25496,7 +25521,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B9" t="n">
         <v>11.0934019859703</v>
@@ -25504,7 +25529,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B10" t="n">
         <v>11.5193520347377</v>
@@ -25512,7 +25537,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B11" t="n">
         <v>10.3976063805748</v>
@@ -25520,7 +25545,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B12" t="n">
         <v>10.203544223433</v>
@@ -25528,7 +25553,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B13" t="n">
         <v>8.25370377873824</v>
@@ -25536,7 +25561,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B14" t="n">
         <v>6.74941660698323</v>
@@ -25544,7 +25569,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B15" t="n">
         <v>6.99352943674983</v>
@@ -25552,7 +25577,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B16" t="n">
         <v>8.54641293280502</v>
@@ -25560,7 +25585,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B17" t="n">
         <v>8.36923199167487</v>
@@ -25568,7 +25593,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B18" t="n">
         <v>8.27326635899438</v>
@@ -25576,7 +25601,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B19" t="n">
         <v>9.85826112039194</v>
@@ -25584,7 +25609,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B20" t="n">
         <v>9.91121604952369</v>
@@ -25592,7 +25617,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B21" t="n">
         <v>10.5072207560502</v>
@@ -25600,7 +25625,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B22" t="n">
         <v>7.79066458038734</v>
@@ -25608,7 +25633,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B23" t="n">
         <v>10.9032596283834</v>
@@ -25616,7 +25641,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B24" t="n">
         <v>8.19610135662233</v>
@@ -25624,7 +25649,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B25" t="n">
         <v>9.07734774781358</v>
@@ -25632,7 +25657,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B26" t="n">
         <v>8.50235678691241</v>
@@ -25640,7 +25665,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B27" t="n">
         <v>9.00143117812621</v>
@@ -25648,7 +25673,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B28" t="n">
         <v>9.09344352882898</v>
@@ -25656,7 +25681,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B29" t="n">
         <v>8.12556120408371</v>
@@ -25664,7 +25689,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B30" t="n">
         <v>10.7444231936402</v>
@@ -25672,7 +25697,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B31" t="n">
         <v>10.0971199004294</v>
@@ -25680,7 +25705,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B32" t="n">
         <v>11.4278274718587</v>
@@ -25688,7 +25713,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B33" t="n">
         <v>12.506561942725</v>
@@ -25696,7 +25721,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B34" t="n">
         <v>14.8525484100527</v>
@@ -25704,7 +25729,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B35" t="n">
         <v>13.9647049646935</v>
@@ -25712,7 +25737,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B36" t="n">
         <v>13.8193035567392</v>
@@ -25720,7 +25745,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B37" t="n">
         <v>14.3299854004434</v>
@@ -25728,7 +25753,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B38" t="n">
         <v>15.3018079241173</v>
@@ -25736,7 +25761,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B39" t="n">
         <v>15.0270385091154</v>
@@ -25744,7 +25769,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B40" t="n">
         <v>13.2518711756956</v>
@@ -25752,7 +25777,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B41" t="n">
         <v>13.1332186179338</v>
@@ -25760,7 +25785,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B42" t="n">
         <v>12.6578401751251</v>
@@ -25768,7 +25793,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B43" t="n">
         <v>11.2954913894953</v>
@@ -25776,7 +25801,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B44" t="n">
         <v>12.7456975920676</v>
@@ -25784,7 +25809,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B45" t="n">
         <v>12.0988566109835</v>
@@ -25792,7 +25817,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B46" t="n">
         <v>12.4954011343489</v>
@@ -25800,7 +25825,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B47" t="n">
         <v>14.2289904200083</v>
@@ -25808,7 +25833,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B48" t="n">
         <v>13.4484012949889</v>
@@ -25816,7 +25841,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B49" t="n">
         <v>15.6988273068042</v>
@@ -25824,7 +25849,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B50" t="n">
         <v>14.2845925451855</v>
@@ -25832,7 +25857,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B51" t="n">
         <v>13.7513624713095</v>
@@ -25840,7 +25865,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B52" t="n">
         <v>16.5561760195999</v>
@@ -25848,7 +25873,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B53" t="n">
         <v>15.9924726433944</v>
@@ -25856,7 +25881,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B54" t="n">
         <v>16.8425831874094</v>
@@ -25864,7 +25889,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B55" t="n">
         <v>16.5276746861153</v>
@@ -25872,7 +25897,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B56" t="n">
         <v>16.4698895002538</v>
@@ -25880,7 +25905,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B57" t="n">
         <v>17.2134250823613</v>
@@ -25888,7 +25913,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B58" t="n">
         <v>15.6816081666631</v>
@@ -25896,7 +25921,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B59" t="n">
         <v>14.8028853950233</v>
@@ -25904,7 +25929,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B60" t="n">
         <v>15.2426482221366</v>
@@ -25912,7 +25937,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B61" t="n">
         <v>15.6902851909184</v>
@@ -25920,7 +25945,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B62" t="n">
         <v>16.5013128950056</v>
@@ -25928,7 +25953,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B63" t="n">
         <v>17.144059922985</v>
@@ -25936,7 +25961,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B64" t="n">
         <v>17.3090733250565</v>
@@ -25944,7 +25969,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B65" t="n">
         <v>19.1915260629344</v>
@@ -25952,7 +25977,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B66" t="n">
         <v>22.7683604016704</v>
@@ -25960,7 +25985,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B67" t="n">
         <v>23.3483213053937</v>
@@ -25968,7 +25993,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B68" t="n">
         <v>23.7330017100268</v>
@@ -25976,7 +26001,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B69" t="n">
         <v>24.5746121277929</v>
@@ -25984,7 +26009,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B70" t="n">
         <v>25.299565253288</v>
@@ -25992,7 +26017,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B71" t="n">
         <v>25.0912717707172</v>
@@ -26000,7 +26025,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B72" t="n">
         <v>23.9521568788769</v>
@@ -26008,7 +26033,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B73" t="n">
         <v>21.1869735832747</v>
@@ -26016,7 +26041,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="B74" t="n">
         <v>20.6527071997174</v>
@@ -26024,7 +26049,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B75" t="n">
         <v>20.1659943690496</v>
@@ -26032,7 +26057,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B76" t="n">
         <v>18.9358160000968</v>
@@ -26040,7 +26065,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B77" t="n">
         <v>16.9203967093089</v>
@@ -26048,7 +26073,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B78" t="n">
         <v>12.907810848208</v>
@@ -26056,7 +26081,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B79" t="n">
         <v>12.4545658937996</v>
@@ -26064,7 +26089,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B80" t="n">
         <v>13.2184526911685</v>
@@ -26072,7 +26097,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B81" t="n">
         <v>14.2594274489356</v>
@@ -26080,7 +26105,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B82" t="n">
         <v>14.1362614616155</v>
@@ -26088,7 +26113,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B83" t="n">
         <v>17.5108308988957</v>
@@ -26096,7 +26121,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B84" t="n">
         <v>17.8203047316368</v>
@@ -26104,7 +26129,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B85" t="n">
         <v>19.6199365813437</v>
@@ -26112,7 +26137,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B86" t="n">
         <v>18.3178769926645</v>
@@ -26120,7 +26145,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B87" t="n">
         <v>16.4922800191838</v>
@@ -26128,7 +26153,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B88" t="n">
         <v>18.0934981429238</v>
@@ -26136,7 +26161,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="B89" t="n">
         <v>14.9717615097796</v>
@@ -26144,7 +26169,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B90" t="n">
         <v>15.137570465284</v>
@@ -26152,7 +26177,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="B91" t="n">
         <v>17.0502997395172</v>
@@ -31012,15 +31037,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B1" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B2" t="n">
         <v>3.02666666666667</v>
@@ -31028,7 +31053,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B3" t="n">
         <v>2.66</v>
@@ -31036,7 +31061,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B4" t="n">
         <v>1.93285714285714</v>
@@ -31044,7 +31069,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="B5" t="n">
         <v>2.59368421052632</v>
@@ -31052,7 +31077,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B6" t="n">
         <v>3.37809523809524</v>
@@ -31060,7 +31085,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="B7" t="n">
         <v>3.61809523809524</v>
@@ -31068,7 +31093,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B8" t="n">
         <v>3.19952380952381</v>
@@ -31076,7 +31101,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B9" t="n">
         <v>3.0585</v>
@@ -31084,7 +31109,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B10" t="n">
         <v>3.20818181818182</v>
@@ -31092,7 +31117,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B11" t="n">
         <v>3.27578947368421</v>
@@ -31100,7 +31125,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B12" t="n">
         <v>3.18227272727273</v>
@@ -31108,7 +31133,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B13" t="n">
         <v>2.79714285714286</v>
@@ -31116,7 +31141,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B14" t="n">
         <v>2.6</v>
@@ -31124,7 +31149,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B15" t="n">
         <v>2.4995652173913</v>
@@ -31132,7 +31157,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B16" t="n">
         <v>2.381</v>
@@ -31140,7 +31165,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="B17" t="n">
         <v>2.52666666666667</v>
@@ -31148,7 +31173,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B18" t="n">
         <v>2.39909090909091</v>
@@ -31156,7 +31181,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="B19" t="n">
         <v>2.73526315789474</v>
@@ -31164,7 +31189,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B20" t="n">
         <v>3.06681818181818</v>
@@ -31172,7 +31197,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="B21" t="n">
         <v>3.0855</v>
@@ -31180,7 +31205,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B22" t="n">
         <v>3.10681818181818</v>
@@ -31188,7 +31213,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B23" t="n">
         <v>3.07421052631579</v>
@@ -31196,7 +31221,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B24" t="n">
         <v>3.31772727272727</v>
@@ -31204,7 +31229,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="B25" t="n">
         <v>4.24</v>
@@ -31212,7 +31237,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B26" t="n">
         <v>5.3725</v>
@@ -31220,7 +31245,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="B27" t="n">
         <v>5.12</v>
@@ -31228,7 +31253,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B28" t="n">
         <v>5.01055555555556</v>
@@ -31236,7 +31261,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B29" t="n">
         <v>4.515</v>
@@ -31244,7 +31269,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B30" t="n">
         <v>3.85909090909091</v>
@@ -31252,7 +31277,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B31" t="n">
         <v>3.835</v>
@@ -31260,7 +31285,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B32" t="n">
         <v>3.83181818181818</v>
@@ -31268,7 +31293,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B33" t="n">
         <v>3.6535</v>
@@ -31276,7 +31301,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B34" t="n">
         <v>3.61904761904762</v>
@@ -31284,7 +31309,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B35" t="n">
         <v>3.5955</v>
@@ -31292,7 +31317,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B36" t="n">
         <v>3.37176470588235</v>
@@ -31300,7 +31325,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B37" t="n">
         <v>3.21842105263158</v>
@@ -31308,7 +31333,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B38" t="n">
         <v>3.37227272727273</v>
@@ -31316,7 +31341,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B39" t="n">
         <v>3.60190476190476</v>
@@ -31324,7 +31349,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B40" t="n">
         <v>3.688</v>
@@ -31332,7 +31357,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="B41" t="n">
         <v>3.55136363636364</v>
@@ -31340,7 +31365,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B42" t="n">
         <v>3.622</v>
@@ -31348,7 +31373,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B43" t="n">
         <v>3.6925</v>
@@ -31356,7 +31381,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B44" t="n">
         <v>3.76</v>
@@ -31364,7 +31389,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B45" t="n">
         <v>3.7965</v>
@@ -31372,7 +31397,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B46" t="n">
         <v>3.8715</v>
@@ -31380,7 +31405,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B47" t="n">
         <v>3.74</v>
@@ -31388,7 +31413,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B48" t="n">
         <v>3.655</v>
@@ -31396,7 +31421,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B49" t="n">
         <v>3.54545454545455</v>
@@ -31404,7 +31429,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B50" t="n">
         <v>3.58952380952381</v>
@@ -31412,7 +31437,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="B51" t="n">
         <v>3.78380952380952</v>
@@ -31420,7 +31445,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B52" t="n">
         <v>3.79809523809524</v>
@@ -31428,7 +31453,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="B53" t="n">
         <v>3.69761904761905</v>
@@ -31436,7 +31461,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B54" t="n">
         <v>3.72315789473684</v>
@@ -31444,7 +31469,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="B55" t="n">
         <v>3.84227272727273</v>
@@ -31452,7 +31477,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B56" t="n">
         <v>3.776</v>
@@ -31460,7 +31485,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="B57" t="n">
         <v>3.7135</v>
@@ -31468,7 +31493,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="B58" t="n">
         <v>3.7004347826087</v>
@@ -31476,7 +31501,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B59" t="n">
         <v>3.655</v>
@@ -31484,7 +31509,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="B60" t="n">
         <v>3.8395</v>
@@ -31492,7 +31517,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B61" t="n">
         <v>3.95363636363636</v>
@@ -31500,7 +31525,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B62" t="n">
         <v>3.98190476190476</v>
@@ -31508,7 +31533,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B63" t="n">
         <v>4.08</v>
@@ -31516,7 +31541,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B64" t="n">
         <v>4.10428571428571</v>
@@ -31524,7 +31549,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B65" t="n">
         <v>4.1465</v>
@@ -31532,7 +31557,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B66" t="n">
         <v>4.17619047619048</v>
@@ -31540,7 +31565,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B67" t="n">
         <v>4.44045454545455</v>
@@ -31548,7 +31573,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="B68" t="n">
         <v>4.59526315789474</v>
@@ -31556,7 +31581,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B69" t="n">
         <v>4.658</v>
@@ -31564,7 +31589,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B70" t="n">
         <v>4.84</v>
@@ -31572,7 +31597,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B71" t="n">
         <v>5.077</v>
@@ -31580,7 +31605,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B72" t="n">
         <v>5.08952380952381</v>
@@ -31588,7 +31613,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B73" t="n">
         <v>5.05090909090909</v>
@@ -31596,7 +31621,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B74" t="n">
         <v>5.06052631578947</v>
@@ -31604,7 +31629,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B75" t="n">
         <v>5.05</v>
@@ -31612,7 +31637,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B76" t="n">
         <v>5.01571428571429</v>
@@ -31620,7 +31645,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B77" t="n">
         <v>5.113</v>
@@ -31628,7 +31653,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B78" t="n">
         <v>5.19619047619048</v>
@@ -31636,7 +31661,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B79" t="n">
         <v>5.071</v>
@@ -31644,7 +31669,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="B80" t="n">
         <v>4.82904761904762</v>
@@ -31652,7 +31677,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B81" t="n">
         <v>4.595</v>
@@ -31660,7 +31685,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B82" t="n">
         <v>4.27045454545455</v>
@@ -31668,7 +31693,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B83" t="n">
         <v>4.0045</v>
@@ -31676,7 +31701,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B84" t="n">
         <v>4.11954545454545</v>
@@ -31684,7 +31709,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B85" t="n">
         <v>4.33722222222222</v>
@@ -31692,7 +31717,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B86" t="n">
         <v>4.273</v>
@@ -31700,7 +31725,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B87" t="n">
         <v>4.32952380952381</v>
@@ -31708,7 +31733,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B88" t="n">
         <v>4.475</v>
@@ -31716,7 +31741,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B89" t="n">
         <v>4.90857142857143</v>
@@ -31724,7 +31749,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B90" t="n">
         <v>5.13904761904762</v>
@@ -31732,7 +31757,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B91" t="n">
         <v>5.753</v>
@@ -31740,7 +31765,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="B92" t="n">
         <v>5.99181818181818</v>
@@ -31748,7 +31773,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B93" t="n">
         <v>6.60666666666667</v>
@@ -31756,7 +31781,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B94" t="n">
         <v>6.92285714285714</v>
@@ -31764,7 +31789,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B95" t="n">
         <v>6.91142857142857</v>
@@ -31772,7 +31797,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B96" t="n">
         <v>6.94714285714286</v>
@@ -31780,7 +31805,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B97" t="n">
         <v>6.7675</v>
@@ -31788,7 +31813,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B98" t="n">
         <v>6.23157894736842</v>
@@ -31796,7 +31821,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B99" t="n">
         <v>5.8</v>
@@ -31804,7 +31829,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B100" t="n">
         <v>5.59</v>
@@ -31812,7 +31837,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B101" t="n">
         <v>5.62636363636364</v>
@@ -31820,7 +31845,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B102" t="n">
         <v>5.6305</v>
@@ -31828,7 +31853,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B103" t="n">
         <v>5.898</v>
@@ -31836,7 +31861,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B104" t="n">
         <v>6.38272727272727</v>
@@ -31844,7 +31869,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B105" t="n">
         <v>6.28842105263158</v>
@@ -31852,7 +31877,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B106" t="n">
         <v>6.60571428571429</v>
@@ -31860,7 +31885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B107" t="n">
         <v>6.67333333333333</v>
@@ -31868,7 +31893,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B108" t="n">
         <v>6.74571428571429</v>
@@ -31876,7 +31901,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B109" t="n">
         <v>6.9905</v>
@@ -31884,7 +31909,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B110" t="n">
         <v>7.44210526315789</v>
@@ -31892,7 +31917,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B111" t="n">
         <v>7.62666666666667</v>
@@ -31900,7 +31925,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B112" t="n">
         <v>7.73761904761905</v>
@@ -31908,7 +31933,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B113" t="n">
         <v>7.68363636363636</v>
@@ -31916,7 +31941,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B114" t="n">
         <v>7.69</v>
@@ -31924,7 +31949,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B115" t="n">
         <v>7.77117647058823</v>
@@ -31932,7 +31957,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B116" t="n">
         <v>7.80666666666667</v>
@@ -31940,7 +31965,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B117" t="n">
         <v>7.718125</v>
@@ -31948,7 +31973,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B118" t="n">
         <v>7.38857142857143</v>
@@ -31956,7 +31981,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B119" t="n">
         <v>6.80947368421053</v>
@@ -31964,7 +31989,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B120" t="n">
         <v>6.57315789473684</v>
@@ -31972,7 +31997,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B121" t="n">
         <v>5.92904761904762</v>
@@ -31980,7 +32005,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B122" t="n">
         <v>5.76611111111111</v>
@@ -31988,7 +32013,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B123" t="n">
         <v>5.676</v>
@@ -31996,7 +32021,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B124" t="n">
         <v>5.46285714285714</v>
@@ -32004,7 +32029,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B125" t="n">
         <v>5.30380952380952</v>
@@ -32012,7 +32037,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B126" t="n">
         <v>4.821875</v>
@@ -32020,7 +32045,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B127" t="n">
         <v>4.46105263157895</v>
@@ -32028,7 +32053,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B128" t="n">
         <v>4.583</v>
@@ -32036,7 +32061,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B129" t="n">
         <v>4.62421052631579</v>
@@ -32044,7 +32069,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B130" t="n">
         <v>3.36818181818182</v>
@@ -32052,7 +32077,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B131" t="n">
         <v>3.07333333333333</v>
@@ -32060,7 +32085,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B132" t="n">
         <v>3.0535</v>
@@ -32068,7 +32093,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B133" t="n">
         <v>3.10954545454545</v>
@@ -32076,7 +32101,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B134" t="n">
         <v>3.54142857142857</v>
@@ -32084,7 +32109,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B135" t="n">
         <v>3.87136363636364</v>
@@ -32092,7 +32117,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B136" t="n">
         <v>3.89666666666667</v>
@@ -32100,7 +32125,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B137" t="n">
         <v>3.848</v>
@@ -32108,7 +32133,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B138" t="n">
         <v>3.33285714285714</v>
@@ -32116,7 +32141,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B139" t="n">
         <v>3.24636363636364</v>
@@ -32124,7 +32149,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B140" t="n">
         <v>3.281</v>
@@ -32132,7 +32157,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B141" t="n">
         <v>3.47789473684211</v>
@@ -32140,7 +32165,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B142" t="n">
         <v>3.4952380952381</v>
@@ -32148,7 +32173,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B143" t="n">
         <v>3.64052631578947</v>
@@ -32156,7 +32181,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B144" t="n">
         <v>3.66952380952381</v>
@@ -32164,7 +32189,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B145" t="n">
         <v>3.61590909090909</v>
@@ -32172,7 +32197,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B146" t="n">
         <v>3.4875</v>
@@ -32180,7 +32205,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B147" t="n">
         <v>3.46</v>
@@ -32188,7 +32213,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B148" t="n">
         <v>3.5605</v>
@@ -32196,7 +32221,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B149" t="n">
         <v>3.56857142857143</v>
@@ -32204,7 +32229,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B150" t="n">
         <v>3.60571428571429</v>
@@ -32212,7 +32237,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B151" t="n">
         <v>3.67736842105263</v>
@@ -32220,7 +32245,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B152" t="n">
         <v>3.77727272727273</v>
@@ -32228,7 +32253,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B153" t="n">
         <v>3.925</v>
@@ -32236,7 +32261,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B154" t="n">
         <v>4.25636363636364</v>
@@ -32244,7 +32269,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B155" t="n">
         <v>4.71444444444444</v>
@@ -32252,7 +32277,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B156" t="n">
         <v>5.10681818181818</v>
@@ -32260,7 +32285,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B157" t="n">
         <v>5.35666666666667</v>
@@ -32268,7 +32293,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B158" t="n">
         <v>5.65285714285714</v>
@@ -32276,7 +32301,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B159" t="n">
         <v>6.01136363636364</v>
@@ -32284,7 +32309,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B160" t="n">
         <v>6.38105263157895</v>
@@ -32292,7 +32317,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B161" t="n">
         <v>6.48545454545455</v>
@@ -32300,7 +32325,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B162" t="n">
         <v>6.45952380952381</v>
@@ -32308,7 +32333,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B163" t="n">
         <v>6.38263157894737</v>
@@ -32316,7 +32341,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B164" t="n">
         <v>6.29090909090909</v>
@@ -32324,7 +32349,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B165" t="n">
         <v>6.1445</v>
@@ -32332,7 +32357,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B166" t="n">
         <v>6.25</v>
@@ -32340,7 +32365,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B167" t="n">
         <v>7.23571428571429</v>
@@ -32348,7 +32373,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B168" t="n">
         <v>8.28</v>
@@ -32356,7 +32381,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B169" t="n">
         <v>8.6555</v>
@@ -32364,7 +32389,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="B170" t="n">
         <v>8.87954545454545</v>
@@ -32372,7 +32397,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B171" t="n">
         <v>9.09666666666667</v>
@@ -32380,7 +32405,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B172" t="n">
         <v>9.026</v>
@@ -32388,7 +32413,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B173" t="n">
         <v>8.63681818181818</v>
@@ -32396,7 +32421,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B174" t="n">
         <v>7.827</v>
@@ -32404,7 +32429,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B175" t="n">
         <v>7.3205</v>
@@ -32412,7 +32437,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B176" t="n">
         <v>6.65090909090909</v>
@@ -32420,7 +32445,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B177" t="n">
         <v>6.351</v>
@@ -32428,7 +32453,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B178" t="n">
         <v>6.277</v>
@@ -32436,7 +32461,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B179" t="n">
         <v>6.49181818181818</v>
@@ -32444,7 +32469,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B180" t="n">
         <v>6.92142857142857</v>
@@ -32452,7 +32477,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B181" t="n">
         <v>6.95285714285714</v>
@@ -32460,7 +32485,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B182" t="n">
         <v>7.22409090909091</v>
@@ -32468,7 +32493,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B183" t="n">
         <v>7.71125</v>
@@ -32476,7 +32501,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B184" t="n">
         <v>8.38380952380952</v>
@@ -32484,7 +32509,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="B185" t="n">
         <v>8.32136363636364</v>
@@ -32492,7 +32517,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B186" t="n">
         <v>8.42105263157895</v>
@@ -32500,7 +32525,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="B187" t="n">
         <v>8.55809523809524</v>
@@ -37356,7 +37381,7 @@
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>1071</v>
+        <v>879</v>
       </c>
       <c r="B794" t="n">
         <v>2.26</v>
@@ -37364,10 +37389,10 @@
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B795" t="n">
-        <v>2.27</v>
+        <v>2.275</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -31023,6 +31023,14 @@
         <v>3.73352052169642</v>
       </c>
     </row>
+    <row r="697">
+      <c r="A697" t="s">
+        <v>878</v>
+      </c>
+      <c r="B697" t="n">
+        <v>3.77861846078164</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -37392,7 +37400,7 @@
         <v>1073</v>
       </c>
       <c r="B795" t="n">
-        <v>2.275</v>
+        <v>2.27909090909091</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -2665,6 +2665,9 @@
     <t xml:space="preserve">Jul 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Aug 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">UnempRate</t>
   </si>
   <si>
@@ -3239,9 +3242,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jun 1968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aug 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Sep 2026</t>
@@ -5845,7 +5845,7 @@
         <v>245</v>
       </c>
       <c r="B245" t="n">
-        <v>72776.1475519244</v>
+        <v>72771.984855698</v>
       </c>
     </row>
     <row r="246">
@@ -5853,7 +5853,7 @@
         <v>246</v>
       </c>
       <c r="B246" t="n">
-        <v>73330.2799266572</v>
+        <v>73340.9143970892</v>
       </c>
     </row>
     <row r="247">
@@ -5861,7 +5861,7 @@
         <v>247</v>
       </c>
       <c r="B247" t="n">
-        <v>73919.8811141678</v>
+        <v>73948.538961422</v>
       </c>
     </row>
     <row r="248">
@@ -5869,7 +5869,7 @@
         <v>248</v>
       </c>
       <c r="B248" t="n">
-        <v>74025.8032662162</v>
+        <v>74034.3642327491</v>
       </c>
     </row>
     <row r="249">
@@ -5877,7 +5877,7 @@
         <v>249</v>
       </c>
       <c r="B249" t="n">
-        <v>73441.9202546755</v>
+        <v>73452.983686921</v>
       </c>
     </row>
     <row r="250">
@@ -5885,7 +5885,7 @@
         <v>250</v>
       </c>
       <c r="B250" t="n">
-        <v>73807.6294696905</v>
+        <v>73852.8651647391</v>
       </c>
     </row>
     <row r="251">
@@ -5893,7 +5893,7 @@
         <v>251</v>
       </c>
       <c r="B251" t="n">
-        <v>73504.9216235631</v>
+        <v>73584.7645804601</v>
       </c>
     </row>
     <row r="252">
@@ -5901,7 +5901,7 @@
         <v>252</v>
       </c>
       <c r="B252" t="n">
-        <v>72950.8775373896</v>
+        <v>72998.9686397036</v>
       </c>
     </row>
     <row r="253">
@@ -5909,7 +5909,7 @@
         <v>253</v>
       </c>
       <c r="B253" t="n">
-        <v>72233.5315890231</v>
+        <v>72284.6427627139</v>
       </c>
     </row>
     <row r="254">
@@ -5917,7 +5917,7 @@
         <v>254</v>
       </c>
       <c r="B254" t="n">
-        <v>72301.0404568269</v>
+        <v>72397.6571214195</v>
       </c>
     </row>
     <row r="255">
@@ -5925,7 +5925,7 @@
         <v>255</v>
       </c>
       <c r="B255" t="n">
-        <v>72418.40357101</v>
+        <v>72556.0023153173</v>
       </c>
     </row>
     <row r="256">
@@ -5933,7 +5933,7 @@
         <v>256</v>
       </c>
       <c r="B256" t="n">
-        <v>72530.2752592198</v>
+        <v>72706.0144196087</v>
       </c>
     </row>
     <row r="257">
@@ -5941,7 +5941,7 @@
         <v>257</v>
       </c>
       <c r="B257" t="n">
-        <v>72630.9995321358</v>
+        <v>72843.4797791874</v>
       </c>
     </row>
     <row r="258">
@@ -5949,7 +5949,7 @@
         <v>258</v>
       </c>
       <c r="B258" t="n">
-        <v>73009.2979675836</v>
+        <v>73253.5598008994</v>
       </c>
     </row>
     <row r="259">
@@ -5957,7 +5957,7 @@
         <v>259</v>
       </c>
       <c r="B259" t="n">
-        <v>72779.795918785</v>
+        <v>72971.1892670949</v>
       </c>
     </row>
     <row r="260">
@@ -5965,7 +5965,7 @@
         <v>260</v>
       </c>
       <c r="B260" t="n">
-        <v>73040.5733646921</v>
+        <v>73115.4782087001</v>
       </c>
     </row>
     <row r="261">
@@ -5973,7 +5973,7 @@
         <v>261</v>
       </c>
       <c r="B261" t="n">
-        <v>72993.8541738573</v>
+        <v>72734.3444834468</v>
       </c>
     </row>
     <row r="262">
@@ -5981,7 +5981,7 @@
         <v>262</v>
       </c>
       <c r="B262" t="n">
-        <v>73235.4395045905</v>
+        <v>72806.0039460692</v>
       </c>
     </row>
     <row r="263">
@@ -5989,7 +5989,7 @@
         <v>263</v>
       </c>
       <c r="B263" t="n">
-        <v>73933.8736094714</v>
+        <v>73400.4191464973</v>
       </c>
     </row>
   </sheetData>
@@ -18977,6 +18977,14 @@
         <v>21214.8</v>
       </c>
     </row>
+    <row r="609">
+      <c r="A609" t="s">
+        <v>881</v>
+      </c>
+      <c r="B609" t="n">
+        <v>21173.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -18994,7 +19002,7 @@
         <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="2">
@@ -23850,6 +23858,14 @@
         <v>880</v>
       </c>
       <c r="B608" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="s">
+        <v>881</v>
+      </c>
+      <c r="B609" t="n">
         <v>6.4</v>
       </c>
     </row>
@@ -23870,7 +23886,7 @@
         <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="2">
@@ -25491,7 +25507,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B204"/>
     </row>
@@ -25512,12 +25528,12 @@
         <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B2" t="n">
         <v>12.9667760753128</v>
@@ -25525,7 +25541,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B3" t="n">
         <v>15.0136942094219</v>
@@ -25533,7 +25549,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B4" t="n">
         <v>15.7173673795166</v>
@@ -25541,7 +25557,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B5" t="n">
         <v>15.0083394292738</v>
@@ -25549,7 +25565,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B6" t="n">
         <v>14.1631513522075</v>
@@ -25557,7 +25573,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B7" t="n">
         <v>14.3196627658395</v>
@@ -25565,7 +25581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B8" t="n">
         <v>14.5659126107761</v>
@@ -25573,7 +25589,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B9" t="n">
         <v>11.0934019859703</v>
@@ -25581,7 +25597,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B10" t="n">
         <v>11.5193520347377</v>
@@ -25589,7 +25605,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B11" t="n">
         <v>10.3976063805748</v>
@@ -25597,7 +25613,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B12" t="n">
         <v>10.203544223433</v>
@@ -25605,7 +25621,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B13" t="n">
         <v>8.25370377873824</v>
@@ -25613,7 +25629,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B14" t="n">
         <v>6.74941660698323</v>
@@ -25621,7 +25637,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B15" t="n">
         <v>6.99352943674983</v>
@@ -25629,7 +25645,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B16" t="n">
         <v>8.54641293280502</v>
@@ -25637,7 +25653,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B17" t="n">
         <v>8.36923199167487</v>
@@ -25645,7 +25661,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B18" t="n">
         <v>8.27326635899438</v>
@@ -25653,7 +25669,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B19" t="n">
         <v>9.85826112039194</v>
@@ -25661,7 +25677,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B20" t="n">
         <v>9.91121604952369</v>
@@ -25669,7 +25685,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B21" t="n">
         <v>10.5072207560502</v>
@@ -25677,7 +25693,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B22" t="n">
         <v>7.79066458038734</v>
@@ -25685,7 +25701,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B23" t="n">
         <v>10.9032596283834</v>
@@ -25693,7 +25709,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B24" t="n">
         <v>8.19610135662233</v>
@@ -25701,7 +25717,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B25" t="n">
         <v>9.07734774781358</v>
@@ -25709,7 +25725,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B26" t="n">
         <v>8.50235678691241</v>
@@ -25717,7 +25733,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B27" t="n">
         <v>9.00143117812621</v>
@@ -25725,7 +25741,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B28" t="n">
         <v>9.09344352882898</v>
@@ -25733,7 +25749,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B29" t="n">
         <v>8.12556120408371</v>
@@ -25741,7 +25757,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B30" t="n">
         <v>10.7444231936402</v>
@@ -25749,7 +25765,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B31" t="n">
         <v>10.0971199004294</v>
@@ -25757,7 +25773,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B32" t="n">
         <v>11.4278274718587</v>
@@ -25765,7 +25781,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B33" t="n">
         <v>12.506561942725</v>
@@ -25773,7 +25789,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B34" t="n">
         <v>14.8525484100527</v>
@@ -25781,7 +25797,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B35" t="n">
         <v>13.9647049646935</v>
@@ -25789,7 +25805,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B36" t="n">
         <v>13.8193035567392</v>
@@ -25797,7 +25813,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B37" t="n">
         <v>14.3299854004434</v>
@@ -25805,7 +25821,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B38" t="n">
         <v>15.3018079241173</v>
@@ -25813,7 +25829,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B39" t="n">
         <v>15.0270385091154</v>
@@ -25821,7 +25837,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B40" t="n">
         <v>13.2518711756956</v>
@@ -25829,7 +25845,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B41" t="n">
         <v>13.1332186179338</v>
@@ -25837,7 +25853,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B42" t="n">
         <v>12.6578401751251</v>
@@ -25845,7 +25861,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B43" t="n">
         <v>11.2954913894953</v>
@@ -25853,7 +25869,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B44" t="n">
         <v>12.7456975920676</v>
@@ -25861,7 +25877,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B45" t="n">
         <v>12.0988566109835</v>
@@ -25869,7 +25885,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B46" t="n">
         <v>12.4954011343489</v>
@@ -25877,7 +25893,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B47" t="n">
         <v>14.2289904200083</v>
@@ -25885,7 +25901,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B48" t="n">
         <v>13.4484012949889</v>
@@ -25893,7 +25909,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B49" t="n">
         <v>15.6988273068042</v>
@@ -25901,7 +25917,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B50" t="n">
         <v>14.2845925451855</v>
@@ -25909,7 +25925,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B51" t="n">
         <v>13.7513624713095</v>
@@ -25917,7 +25933,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B52" t="n">
         <v>16.5561760195999</v>
@@ -25925,7 +25941,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B53" t="n">
         <v>15.9924726433944</v>
@@ -25933,7 +25949,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B54" t="n">
         <v>16.8425831874094</v>
@@ -25941,7 +25957,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B55" t="n">
         <v>16.5276746861153</v>
@@ -25949,7 +25965,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B56" t="n">
         <v>16.4698895002538</v>
@@ -25957,7 +25973,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B57" t="n">
         <v>17.2134250823613</v>
@@ -25965,7 +25981,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B58" t="n">
         <v>15.6816081666631</v>
@@ -25973,7 +25989,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B59" t="n">
         <v>14.8028853950233</v>
@@ -25981,7 +25997,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B60" t="n">
         <v>15.2426482221366</v>
@@ -25989,7 +26005,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B61" t="n">
         <v>15.6902851909184</v>
@@ -25997,7 +26013,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B62" t="n">
         <v>16.5013128950056</v>
@@ -26005,7 +26021,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B63" t="n">
         <v>17.144059922985</v>
@@ -26013,7 +26029,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B64" t="n">
         <v>17.3090733250565</v>
@@ -26021,7 +26037,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B65" t="n">
         <v>19.1915260629344</v>
@@ -26029,7 +26045,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B66" t="n">
         <v>22.7683604016704</v>
@@ -26037,7 +26053,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B67" t="n">
         <v>23.3483213053937</v>
@@ -26045,7 +26061,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B68" t="n">
         <v>23.7330017100268</v>
@@ -26053,7 +26069,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B69" t="n">
         <v>24.5746121277929</v>
@@ -26061,7 +26077,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B70" t="n">
         <v>25.299565253288</v>
@@ -26069,7 +26085,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B71" t="n">
         <v>25.0912717707172</v>
@@ -26077,7 +26093,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B72" t="n">
         <v>23.9521568788769</v>
@@ -26085,7 +26101,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B73" t="n">
         <v>21.1869735832747</v>
@@ -26093,7 +26109,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B74" t="n">
         <v>20.6527071997174</v>
@@ -26101,7 +26117,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B75" t="n">
         <v>20.1659943690496</v>
@@ -26109,7 +26125,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B76" t="n">
         <v>18.9358160000968</v>
@@ -26117,7 +26133,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B77" t="n">
         <v>16.9203967093089</v>
@@ -26125,7 +26141,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B78" t="n">
         <v>12.907810848208</v>
@@ -26133,7 +26149,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B79" t="n">
         <v>12.4545658937996</v>
@@ -26141,7 +26157,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B80" t="n">
         <v>13.2184526911685</v>
@@ -26149,7 +26165,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B81" t="n">
         <v>14.2594274489356</v>
@@ -26157,7 +26173,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B82" t="n">
         <v>14.1362614616155</v>
@@ -26165,7 +26181,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B83" t="n">
         <v>17.5108308988957</v>
@@ -26173,7 +26189,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B84" t="n">
         <v>17.8203047316368</v>
@@ -26181,7 +26197,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B85" t="n">
         <v>19.6199365813437</v>
@@ -26189,7 +26205,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B86" t="n">
         <v>18.3178769926645</v>
@@ -26197,7 +26213,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B87" t="n">
         <v>16.4922800191838</v>
@@ -26205,7 +26221,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B88" t="n">
         <v>18.0934981429238</v>
@@ -26213,7 +26229,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B89" t="n">
         <v>14.9717615097796</v>
@@ -26221,7 +26237,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B90" t="n">
         <v>15.137570465284</v>
@@ -26229,7 +26245,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B91" t="n">
         <v>17.0502997395172</v>
@@ -30560,7 +30576,7 @@
         <v>814</v>
       </c>
       <c r="B632" t="n">
-        <v>10.2014270302325</v>
+        <v>10.2641419322758</v>
       </c>
     </row>
     <row r="633">
@@ -30568,7 +30584,7 @@
         <v>815</v>
       </c>
       <c r="B633" t="n">
-        <v>9.13417916746047</v>
+        <v>9.12828914650481</v>
       </c>
     </row>
     <row r="634">
@@ -30576,7 +30592,7 @@
         <v>816</v>
       </c>
       <c r="B634" t="n">
-        <v>7.91057910356393</v>
+        <v>7.83519431090747</v>
       </c>
     </row>
     <row r="635">
@@ -30584,7 +30600,7 @@
         <v>817</v>
       </c>
       <c r="B635" t="n">
-        <v>8.71374138223431</v>
+        <v>8.67988470225648</v>
       </c>
     </row>
     <row r="636">
@@ -30592,7 +30608,7 @@
         <v>818</v>
       </c>
       <c r="B636" t="n">
-        <v>9.30931842399314</v>
+        <v>9.35642121683543</v>
       </c>
     </row>
     <row r="637">
@@ -30600,7 +30616,7 @@
         <v>819</v>
       </c>
       <c r="B637" t="n">
-        <v>9.55728774659724</v>
+        <v>9.58411725365131</v>
       </c>
     </row>
     <row r="638">
@@ -30608,7 +30624,7 @@
         <v>820</v>
       </c>
       <c r="B638" t="n">
-        <v>10.2699276736572</v>
+        <v>10.2196761430398</v>
       </c>
     </row>
     <row r="639">
@@ -30616,7 +30632,7 @@
         <v>821</v>
       </c>
       <c r="B639" t="n">
-        <v>9.95076410241623</v>
+        <v>9.76819428464749</v>
       </c>
     </row>
     <row r="640">
@@ -30624,7 +30640,7 @@
         <v>822</v>
       </c>
       <c r="B640" t="n">
-        <v>9.36404279467786</v>
+        <v>9.16290782785741</v>
       </c>
     </row>
     <row r="641">
@@ -30632,7 +30648,7 @@
         <v>823</v>
       </c>
       <c r="B641" t="n">
-        <v>6.62904316779314</v>
+        <v>7.11838875141681</v>
       </c>
     </row>
     <row r="642">
@@ -30640,7 +30656,7 @@
         <v>824</v>
       </c>
       <c r="B642" t="n">
-        <v>6.48632593655972</v>
+        <v>6.21548576107471</v>
       </c>
     </row>
     <row r="643">
@@ -30648,7 +30664,7 @@
         <v>825</v>
       </c>
       <c r="B643" t="n">
-        <v>5.86831030736363</v>
+        <v>5.85083353116229</v>
       </c>
     </row>
     <row r="644">
@@ -30656,7 +30672,7 @@
         <v>826</v>
       </c>
       <c r="B644" t="n">
-        <v>4.84028698945146</v>
+        <v>4.85412679462777</v>
       </c>
     </row>
     <row r="645">
@@ -30664,7 +30680,7 @@
         <v>827</v>
       </c>
       <c r="B645" t="n">
-        <v>4.47097022567251</v>
+        <v>4.62575644452616</v>
       </c>
     </row>
     <row r="646">
@@ -30672,7 +30688,7 @@
         <v>828</v>
       </c>
       <c r="B646" t="n">
-        <v>4.91530375126075</v>
+        <v>5.10971115943115</v>
       </c>
     </row>
     <row r="647">
@@ -30680,7 +30696,7 @@
         <v>829</v>
       </c>
       <c r="B647" t="n">
-        <v>5.59020250461025</v>
+        <v>5.06088856394058</v>
       </c>
     </row>
     <row r="648">
@@ -30688,7 +30704,7 @@
         <v>830</v>
       </c>
       <c r="B648" t="n">
-        <v>4.63495069217423</v>
+        <v>4.79232942306266</v>
       </c>
     </row>
     <row r="649">
@@ -30696,7 +30712,7 @@
         <v>831</v>
       </c>
       <c r="B649" t="n">
-        <v>4.97085923087823</v>
+        <v>5.01149062097626</v>
       </c>
     </row>
     <row r="650">
@@ -30704,7 +30720,7 @@
         <v>832</v>
       </c>
       <c r="B650" t="n">
-        <v>4.70683945720762</v>
+        <v>4.65576867137999</v>
       </c>
     </row>
     <row r="651">
@@ -30712,7 +30728,7 @@
         <v>833</v>
       </c>
       <c r="B651" t="n">
-        <v>3.49065407108487</v>
+        <v>3.22041962113615</v>
       </c>
     </row>
     <row r="652">
@@ -30720,7 +30736,7 @@
         <v>834</v>
       </c>
       <c r="B652" t="n">
-        <v>4.22898660683993</v>
+        <v>3.86839368417324</v>
       </c>
     </row>
     <row r="653">
@@ -30728,7 +30744,7 @@
         <v>835</v>
       </c>
       <c r="B653" t="n">
-        <v>3.12169101651319</v>
+        <v>3.6197632975251</v>
       </c>
     </row>
     <row r="654">
@@ -30736,7 +30752,7 @@
         <v>836</v>
       </c>
       <c r="B654" t="n">
-        <v>3.00518746317494</v>
+        <v>2.86773724659947</v>
       </c>
     </row>
     <row r="655">
@@ -30744,7 +30760,7 @@
         <v>837</v>
       </c>
       <c r="B655" t="n">
-        <v>3.30231678017797</v>
+        <v>3.21922190388996</v>
       </c>
     </row>
     <row r="656">
@@ -30752,7 +30768,7 @@
         <v>838</v>
       </c>
       <c r="B656" t="n">
-        <v>3.91268486330936</v>
+        <v>3.90346484855299</v>
       </c>
     </row>
     <row r="657">
@@ -30760,7 +30776,7 @@
         <v>839</v>
       </c>
       <c r="B657" t="n">
-        <v>4.66159557275232</v>
+        <v>4.93283878049056</v>
       </c>
     </row>
     <row r="658">
@@ -30768,7 +30784,7 @@
         <v>840</v>
       </c>
       <c r="B658" t="n">
-        <v>3.37688052620531</v>
+        <v>3.80217861606346</v>
       </c>
     </row>
     <row r="659">
@@ -30776,7 +30792,7 @@
         <v>841</v>
       </c>
       <c r="B659" t="n">
-        <v>4.56582918323637</v>
+        <v>4.14244757678489</v>
       </c>
     </row>
     <row r="660">
@@ -30784,7 +30800,7 @@
         <v>842</v>
       </c>
       <c r="B660" t="n">
-        <v>3.83094523215118</v>
+        <v>3.88974161608896</v>
       </c>
     </row>
     <row r="661">
@@ -30792,7 +30808,7 @@
         <v>843</v>
       </c>
       <c r="B661" t="n">
-        <v>2.66057774716916</v>
+        <v>2.70547567057602</v>
       </c>
     </row>
     <row r="662">
@@ -30800,7 +30816,7 @@
         <v>844</v>
       </c>
       <c r="B662" t="n">
-        <v>2.75684281480171</v>
+        <v>2.69393672744384</v>
       </c>
     </row>
     <row r="663">
@@ -30808,7 +30824,7 @@
         <v>845</v>
       </c>
       <c r="B663" t="n">
-        <v>3.47206900850163</v>
+        <v>3.19441624235593</v>
       </c>
     </row>
     <row r="664">
@@ -30816,7 +30832,7 @@
         <v>846</v>
       </c>
       <c r="B664" t="n">
-        <v>4.49302785528737</v>
+        <v>3.90919896558633</v>
       </c>
     </row>
     <row r="665">
@@ -30824,7 +30840,7 @@
         <v>847</v>
       </c>
       <c r="B665" t="n">
-        <v>4.28512320015062</v>
+        <v>4.64811973110322</v>
       </c>
     </row>
     <row r="666">
@@ -30832,7 +30848,7 @@
         <v>848</v>
       </c>
       <c r="B666" t="n">
-        <v>6.00937726123868</v>
+        <v>6.03597520573892</v>
       </c>
     </row>
     <row r="667">
@@ -30840,7 +30856,7 @@
         <v>849</v>
       </c>
       <c r="B667" t="n">
-        <v>6.32487180196061</v>
+        <v>6.32301662689481</v>
       </c>
     </row>
     <row r="668">
@@ -30848,7 +30864,7 @@
         <v>850</v>
       </c>
       <c r="B668" t="n">
-        <v>5.20814692429619</v>
+        <v>5.19885765446613</v>
       </c>
     </row>
     <row r="669">
@@ -30856,7 +30872,7 @@
         <v>851</v>
       </c>
       <c r="B669" t="n">
-        <v>4.43643458493724</v>
+        <v>4.69300223728489</v>
       </c>
     </row>
     <row r="670">
@@ -30864,7 +30880,7 @@
         <v>852</v>
       </c>
       <c r="B670" t="n">
-        <v>3.82852011648303</v>
+        <v>4.46867492752265</v>
       </c>
     </row>
     <row r="671">
@@ -30872,7 +30888,7 @@
         <v>853</v>
       </c>
       <c r="B671" t="n">
-        <v>4.57099888619846</v>
+        <v>4.01511528185554</v>
       </c>
     </row>
     <row r="672">
@@ -30880,7 +30896,7 @@
         <v>854</v>
       </c>
       <c r="B672" t="n">
-        <v>4.35084148405768</v>
+        <v>4.36485625209614</v>
       </c>
     </row>
     <row r="673">
@@ -30888,7 +30904,7 @@
         <v>855</v>
       </c>
       <c r="B673" t="n">
-        <v>5.47223314279404</v>
+        <v>5.53162070719077</v>
       </c>
     </row>
     <row r="674">
@@ -30896,7 +30912,7 @@
         <v>856</v>
       </c>
       <c r="B674" t="n">
-        <v>6.41013784488794</v>
+        <v>6.22692020042219</v>
       </c>
     </row>
     <row r="675">
@@ -30904,7 +30920,7 @@
         <v>857</v>
       </c>
       <c r="B675" t="n">
-        <v>6.33172107126688</v>
+        <v>6.14903648331157</v>
       </c>
     </row>
     <row r="676">
@@ -30912,7 +30928,7 @@
         <v>858</v>
       </c>
       <c r="B676" t="n">
-        <v>6.51834044955629</v>
+        <v>5.89133478060058</v>
       </c>
     </row>
     <row r="677">
@@ -30920,7 +30936,7 @@
         <v>859</v>
       </c>
       <c r="B677" t="n">
-        <v>6.73910668131498</v>
+        <v>7.25778223721586</v>
       </c>
     </row>
     <row r="678">
@@ -30928,7 +30944,7 @@
         <v>860</v>
       </c>
       <c r="B678" t="n">
-        <v>6.18827296964122</v>
+        <v>6.24975685099722</v>
       </c>
     </row>
     <row r="679">
@@ -30936,7 +30952,7 @@
         <v>861</v>
       </c>
       <c r="B679" t="n">
-        <v>5.58429509750073</v>
+        <v>5.51813851850075</v>
       </c>
     </row>
     <row r="680">
@@ -30944,7 +30960,7 @@
         <v>862</v>
       </c>
       <c r="B680" t="n">
-        <v>6.10974674518887</v>
+        <v>6.44822265682045</v>
       </c>
     </row>
     <row r="681">
@@ -30952,7 +30968,7 @@
         <v>863</v>
       </c>
       <c r="B681" t="n">
-        <v>6.60271918872614</v>
+        <v>6.85477086513787</v>
       </c>
     </row>
     <row r="682">
@@ -30960,7 +30976,7 @@
         <v>864</v>
       </c>
       <c r="B682" t="n">
-        <v>6.42688175654435</v>
+        <v>7.11755533751682</v>
       </c>
     </row>
     <row r="683">
@@ -30968,7 +30984,7 @@
         <v>865</v>
       </c>
       <c r="B683" t="n">
-        <v>6.02917181563913</v>
+        <v>5.59938427670487</v>
       </c>
     </row>
     <row r="684">
@@ -30976,7 +30992,7 @@
         <v>866</v>
       </c>
       <c r="B684" t="n">
-        <v>5.80374444730647</v>
+        <v>5.77074995107162</v>
       </c>
     </row>
     <row r="685">
@@ -30984,7 +31000,7 @@
         <v>867</v>
       </c>
       <c r="B685" t="n">
-        <v>5.13934779897651</v>
+        <v>5.21828672845826</v>
       </c>
     </row>
     <row r="686">
@@ -30992,7 +31008,7 @@
         <v>868</v>
       </c>
       <c r="B686" t="n">
-        <v>3.99543378532705</v>
+        <v>3.72549504483491</v>
       </c>
     </row>
     <row r="687">
@@ -31000,7 +31016,7 @@
         <v>869</v>
       </c>
       <c r="B687" t="n">
-        <v>4.15106011934001</v>
+        <v>4.04290972055758</v>
       </c>
     </row>
     <row r="688">
@@ -31008,7 +31024,7 @@
         <v>870</v>
       </c>
       <c r="B688" t="n">
-        <v>4.02928417787216</v>
+        <v>3.29047281898694</v>
       </c>
     </row>
     <row r="689">
@@ -31016,7 +31032,7 @@
         <v>871</v>
       </c>
       <c r="B689" t="n">
-        <v>3.85246443943114</v>
+        <v>4.34998864218635</v>
       </c>
     </row>
     <row r="690">
@@ -31024,7 +31040,7 @@
         <v>872</v>
       </c>
       <c r="B690" t="n">
-        <v>3.96590181275134</v>
+        <v>4.15122701803687</v>
       </c>
     </row>
     <row r="691">
@@ -31032,7 +31048,7 @@
         <v>873</v>
       </c>
       <c r="B691" t="n">
-        <v>4.25945242145825</v>
+        <v>4.17569318913718</v>
       </c>
     </row>
     <row r="692">
@@ -31040,7 +31056,7 @@
         <v>874</v>
       </c>
       <c r="B692" t="n">
-        <v>3.96183803700372</v>
+        <v>4.27576061238923</v>
       </c>
     </row>
     <row r="693">
@@ -31048,7 +31064,7 @@
         <v>875</v>
       </c>
       <c r="B693" t="n">
-        <v>3.28495530397491</v>
+        <v>3.43034302949804</v>
       </c>
     </row>
     <row r="694">
@@ -31056,7 +31072,7 @@
         <v>876</v>
       </c>
       <c r="B694" t="n">
-        <v>3.26228113563431</v>
+        <v>3.97864044098481</v>
       </c>
     </row>
     <row r="695">
@@ -31064,7 +31080,7 @@
         <v>877</v>
       </c>
       <c r="B695" t="n">
-        <v>3.7862858229753</v>
+        <v>3.19310024789546</v>
       </c>
     </row>
     <row r="696">
@@ -31072,7 +31088,7 @@
         <v>878</v>
       </c>
       <c r="B696" t="n">
-        <v>3.73352052169642</v>
+        <v>3.48048979642224</v>
       </c>
     </row>
     <row r="697">
@@ -31080,7 +31096,15 @@
         <v>879</v>
       </c>
       <c r="B697" t="n">
-        <v>3.77861846078164</v>
+        <v>3.97951174767991</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="s">
+        <v>880</v>
+      </c>
+      <c r="B698" t="n">
+        <v>4.50630703874581</v>
       </c>
     </row>
   </sheetData>
@@ -31097,15 +31121,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B2" t="n">
         <v>3.02666666666667</v>
@@ -31113,7 +31137,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B3" t="n">
         <v>2.66</v>
@@ -31121,7 +31145,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B4" t="n">
         <v>1.93285714285714</v>
@@ -31129,7 +31153,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B5" t="n">
         <v>2.59368421052632</v>
@@ -31137,7 +31161,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B6" t="n">
         <v>3.37809523809524</v>
@@ -31145,7 +31169,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B7" t="n">
         <v>3.61809523809524</v>
@@ -31153,7 +31177,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B8" t="n">
         <v>3.19952380952381</v>
@@ -31161,7 +31185,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B9" t="n">
         <v>3.0585</v>
@@ -31169,7 +31193,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B10" t="n">
         <v>3.20818181818182</v>
@@ -31177,7 +31201,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B11" t="n">
         <v>3.27578947368421</v>
@@ -31185,7 +31209,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B12" t="n">
         <v>3.18227272727273</v>
@@ -31193,7 +31217,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B13" t="n">
         <v>2.79714285714286</v>
@@ -31201,7 +31225,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B14" t="n">
         <v>2.6</v>
@@ -31209,7 +31233,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B15" t="n">
         <v>2.4995652173913</v>
@@ -31217,7 +31241,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B16" t="n">
         <v>2.381</v>
@@ -31225,7 +31249,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B17" t="n">
         <v>2.52666666666667</v>
@@ -31233,7 +31257,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B18" t="n">
         <v>2.39909090909091</v>
@@ -31241,7 +31265,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B19" t="n">
         <v>2.73526315789474</v>
@@ -31249,7 +31273,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B20" t="n">
         <v>3.06681818181818</v>
@@ -31257,7 +31281,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B21" t="n">
         <v>3.0855</v>
@@ -31265,7 +31289,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B22" t="n">
         <v>3.10681818181818</v>
@@ -31273,7 +31297,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B23" t="n">
         <v>3.07421052631579</v>
@@ -31281,7 +31305,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B24" t="n">
         <v>3.31772727272727</v>
@@ -31289,7 +31313,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B25" t="n">
         <v>4.24</v>
@@ -31297,7 +31321,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B26" t="n">
         <v>5.3725</v>
@@ -31305,7 +31329,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B27" t="n">
         <v>5.12</v>
@@ -31313,7 +31337,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B28" t="n">
         <v>5.01055555555556</v>
@@ -31321,7 +31345,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B29" t="n">
         <v>4.515</v>
@@ -31329,7 +31353,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B30" t="n">
         <v>3.85909090909091</v>
@@ -31337,7 +31361,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B31" t="n">
         <v>3.835</v>
@@ -31345,7 +31369,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B32" t="n">
         <v>3.83181818181818</v>
@@ -31353,7 +31377,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B33" t="n">
         <v>3.6535</v>
@@ -31361,7 +31385,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B34" t="n">
         <v>3.61904761904762</v>
@@ -31369,7 +31393,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B35" t="n">
         <v>3.5955</v>
@@ -31377,7 +31401,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B36" t="n">
         <v>3.37176470588235</v>
@@ -31385,7 +31409,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B37" t="n">
         <v>3.21842105263158</v>
@@ -31393,7 +31417,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B38" t="n">
         <v>3.37227272727273</v>
@@ -31401,7 +31425,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B39" t="n">
         <v>3.60190476190476</v>
@@ -31409,7 +31433,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B40" t="n">
         <v>3.688</v>
@@ -31417,7 +31441,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B41" t="n">
         <v>3.55136363636364</v>
@@ -31425,7 +31449,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B42" t="n">
         <v>3.622</v>
@@ -31433,7 +31457,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B43" t="n">
         <v>3.6925</v>
@@ -31441,7 +31465,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B44" t="n">
         <v>3.76</v>
@@ -31449,7 +31473,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B45" t="n">
         <v>3.7965</v>
@@ -31457,7 +31481,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B46" t="n">
         <v>3.8715</v>
@@ -31465,7 +31489,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B47" t="n">
         <v>3.74</v>
@@ -31473,7 +31497,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B48" t="n">
         <v>3.655</v>
@@ -31481,7 +31505,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B49" t="n">
         <v>3.54545454545455</v>
@@ -31489,7 +31513,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B50" t="n">
         <v>3.58952380952381</v>
@@ -31497,7 +31521,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B51" t="n">
         <v>3.78380952380952</v>
@@ -31505,7 +31529,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B52" t="n">
         <v>3.79809523809524</v>
@@ -31513,7 +31537,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B53" t="n">
         <v>3.69761904761905</v>
@@ -31521,7 +31545,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B54" t="n">
         <v>3.72315789473684</v>
@@ -31529,7 +31553,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B55" t="n">
         <v>3.84227272727273</v>
@@ -31537,7 +31561,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B56" t="n">
         <v>3.776</v>
@@ -31545,7 +31569,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B57" t="n">
         <v>3.7135</v>
@@ -31553,7 +31577,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B58" t="n">
         <v>3.7004347826087</v>
@@ -31561,7 +31585,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B59" t="n">
         <v>3.655</v>
@@ -31569,7 +31593,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B60" t="n">
         <v>3.8395</v>
@@ -31577,7 +31601,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B61" t="n">
         <v>3.95363636363636</v>
@@ -31585,7 +31609,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B62" t="n">
         <v>3.98190476190476</v>
@@ -31593,7 +31617,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B63" t="n">
         <v>4.08</v>
@@ -31601,7 +31625,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B64" t="n">
         <v>4.10428571428571</v>
@@ -31609,7 +31633,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B65" t="n">
         <v>4.1465</v>
@@ -31617,7 +31641,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B66" t="n">
         <v>4.17619047619048</v>
@@ -31625,7 +31649,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B67" t="n">
         <v>4.44045454545455</v>
@@ -31633,7 +31657,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B68" t="n">
         <v>4.59526315789474</v>
@@ -31641,7 +31665,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B69" t="n">
         <v>4.658</v>
@@ -31649,7 +31673,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B70" t="n">
         <v>4.84</v>
@@ -31657,7 +31681,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B71" t="n">
         <v>5.077</v>
@@ -31665,7 +31689,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B72" t="n">
         <v>5.08952380952381</v>
@@ -31673,7 +31697,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B73" t="n">
         <v>5.05090909090909</v>
@@ -31681,7 +31705,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B74" t="n">
         <v>5.06052631578947</v>
@@ -31689,7 +31713,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B75" t="n">
         <v>5.05</v>
@@ -31697,7 +31721,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B76" t="n">
         <v>5.01571428571429</v>
@@ -31705,7 +31729,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B77" t="n">
         <v>5.113</v>
@@ -31713,7 +31737,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B78" t="n">
         <v>5.19619047619048</v>
@@ -31721,7 +31745,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B79" t="n">
         <v>5.071</v>
@@ -31729,7 +31753,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B80" t="n">
         <v>4.82904761904762</v>
@@ -31737,7 +31761,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B81" t="n">
         <v>4.595</v>
@@ -31745,7 +31769,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B82" t="n">
         <v>4.27045454545455</v>
@@ -31753,7 +31777,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B83" t="n">
         <v>4.0045</v>
@@ -31761,7 +31785,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B84" t="n">
         <v>4.11954545454545</v>
@@ -31769,7 +31793,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B85" t="n">
         <v>4.33722222222222</v>
@@ -31777,7 +31801,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B86" t="n">
         <v>4.273</v>
@@ -31785,7 +31809,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B87" t="n">
         <v>4.32952380952381</v>
@@ -31793,7 +31817,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B88" t="n">
         <v>4.475</v>
@@ -31801,7 +31825,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B89" t="n">
         <v>4.90857142857143</v>
@@ -31809,7 +31833,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B90" t="n">
         <v>5.13904761904762</v>
@@ -31817,7 +31841,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B91" t="n">
         <v>5.753</v>
@@ -31825,7 +31849,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B92" t="n">
         <v>5.99181818181818</v>
@@ -31833,7 +31857,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B93" t="n">
         <v>6.60666666666667</v>
@@ -31841,7 +31865,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B94" t="n">
         <v>6.92285714285714</v>
@@ -31849,7 +31873,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B95" t="n">
         <v>6.91142857142857</v>
@@ -31857,7 +31881,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B96" t="n">
         <v>6.94714285714286</v>
@@ -31865,7 +31889,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B97" t="n">
         <v>6.7675</v>
@@ -31873,7 +31897,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B98" t="n">
         <v>6.23157894736842</v>
@@ -31881,7 +31905,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B99" t="n">
         <v>5.8</v>
@@ -31889,7 +31913,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B100" t="n">
         <v>5.59</v>
@@ -31897,7 +31921,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B101" t="n">
         <v>5.62636363636364</v>
@@ -31905,7 +31929,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B102" t="n">
         <v>5.6305</v>
@@ -31913,7 +31937,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B103" t="n">
         <v>5.898</v>
@@ -31921,7 +31945,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B104" t="n">
         <v>6.38272727272727</v>
@@ -31929,7 +31953,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B105" t="n">
         <v>6.28842105263158</v>
@@ -31937,7 +31961,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B106" t="n">
         <v>6.60571428571429</v>
@@ -31945,7 +31969,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B107" t="n">
         <v>6.67333333333333</v>
@@ -31953,7 +31977,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B108" t="n">
         <v>6.74571428571429</v>
@@ -31961,7 +31985,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B109" t="n">
         <v>6.9905</v>
@@ -31969,7 +31993,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B110" t="n">
         <v>7.44210526315789</v>
@@ -31977,7 +32001,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B111" t="n">
         <v>7.62666666666667</v>
@@ -31985,7 +32009,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B112" t="n">
         <v>7.73761904761905</v>
@@ -31993,7 +32017,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B113" t="n">
         <v>7.68363636363636</v>
@@ -32001,7 +32025,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B114" t="n">
         <v>7.69</v>
@@ -32009,7 +32033,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B115" t="n">
         <v>7.77117647058823</v>
@@ -32017,7 +32041,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B116" t="n">
         <v>7.80666666666667</v>
@@ -32025,7 +32049,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B117" t="n">
         <v>7.718125</v>
@@ -32033,7 +32057,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B118" t="n">
         <v>7.38857142857143</v>
@@ -32041,7 +32065,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B119" t="n">
         <v>6.80947368421053</v>
@@ -32049,7 +32073,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B120" t="n">
         <v>6.57315789473684</v>
@@ -32057,7 +32081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B121" t="n">
         <v>5.92904761904762</v>
@@ -32065,7 +32089,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B122" t="n">
         <v>5.76611111111111</v>
@@ -32073,7 +32097,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B123" t="n">
         <v>5.676</v>
@@ -32081,7 +32105,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B124" t="n">
         <v>5.46285714285714</v>
@@ -32089,7 +32113,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B125" t="n">
         <v>5.30380952380952</v>
@@ -32097,7 +32121,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B126" t="n">
         <v>4.821875</v>
@@ -32105,7 +32129,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B127" t="n">
         <v>4.46105263157895</v>
@@ -32113,7 +32137,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B128" t="n">
         <v>4.583</v>
@@ -32121,7 +32145,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B129" t="n">
         <v>4.62421052631579</v>
@@ -32129,7 +32153,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B130" t="n">
         <v>3.36818181818182</v>
@@ -32137,7 +32161,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B131" t="n">
         <v>3.07333333333333</v>
@@ -32145,7 +32169,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B132" t="n">
         <v>3.0535</v>
@@ -32153,7 +32177,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B133" t="n">
         <v>3.10954545454545</v>
@@ -32161,7 +32185,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B134" t="n">
         <v>3.54142857142857</v>
@@ -32169,7 +32193,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B135" t="n">
         <v>3.87136363636364</v>
@@ -32177,7 +32201,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B136" t="n">
         <v>3.89666666666667</v>
@@ -32185,7 +32209,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B137" t="n">
         <v>3.848</v>
@@ -32193,7 +32217,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B138" t="n">
         <v>3.33285714285714</v>
@@ -32201,7 +32225,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B139" t="n">
         <v>3.24636363636364</v>
@@ -32209,7 +32233,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B140" t="n">
         <v>3.281</v>
@@ -32217,7 +32241,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B141" t="n">
         <v>3.47789473684211</v>
@@ -32225,7 +32249,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B142" t="n">
         <v>3.4952380952381</v>
@@ -32233,7 +32257,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B143" t="n">
         <v>3.64052631578947</v>
@@ -32241,7 +32265,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B144" t="n">
         <v>3.66952380952381</v>
@@ -32249,7 +32273,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B145" t="n">
         <v>3.61590909090909</v>
@@ -32257,7 +32281,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B146" t="n">
         <v>3.4875</v>
@@ -32265,7 +32289,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B147" t="n">
         <v>3.46</v>
@@ -32273,7 +32297,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B148" t="n">
         <v>3.5605</v>
@@ -32281,7 +32305,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B149" t="n">
         <v>3.56857142857143</v>
@@ -32289,7 +32313,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B150" t="n">
         <v>3.60571428571429</v>
@@ -32297,7 +32321,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B151" t="n">
         <v>3.67736842105263</v>
@@ -32305,7 +32329,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B152" t="n">
         <v>3.77727272727273</v>
@@ -32313,7 +32337,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B153" t="n">
         <v>3.925</v>
@@ -32321,7 +32345,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B154" t="n">
         <v>4.25636363636364</v>
@@ -32329,7 +32353,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B155" t="n">
         <v>4.71444444444444</v>
@@ -32337,7 +32361,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B156" t="n">
         <v>5.10681818181818</v>
@@ -32345,7 +32369,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B157" t="n">
         <v>5.35666666666667</v>
@@ -32353,7 +32377,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B158" t="n">
         <v>5.65285714285714</v>
@@ -32361,7 +32385,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B159" t="n">
         <v>6.01136363636364</v>
@@ -32369,7 +32393,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B160" t="n">
         <v>6.38105263157895</v>
@@ -32377,7 +32401,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B161" t="n">
         <v>6.48545454545455</v>
@@ -32385,7 +32409,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B162" t="n">
         <v>6.45952380952381</v>
@@ -32393,7 +32417,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B163" t="n">
         <v>6.38263157894737</v>
@@ -32401,7 +32425,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B164" t="n">
         <v>6.29090909090909</v>
@@ -32409,7 +32433,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B165" t="n">
         <v>6.1445</v>
@@ -32417,7 +32441,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B166" t="n">
         <v>6.25</v>
@@ -32425,7 +32449,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B167" t="n">
         <v>7.23571428571429</v>
@@ -32433,7 +32457,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B168" t="n">
         <v>8.28</v>
@@ -32441,7 +32465,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B169" t="n">
         <v>8.6555</v>
@@ -32449,7 +32473,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B170" t="n">
         <v>8.87954545454545</v>
@@ -32457,7 +32481,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B171" t="n">
         <v>9.09666666666667</v>
@@ -32465,7 +32489,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B172" t="n">
         <v>9.026</v>
@@ -32473,7 +32497,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B173" t="n">
         <v>8.63681818181818</v>
@@ -32481,7 +32505,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B174" t="n">
         <v>7.827</v>
@@ -32489,7 +32513,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B175" t="n">
         <v>7.3205</v>
@@ -32497,7 +32521,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B176" t="n">
         <v>6.65090909090909</v>
@@ -32505,7 +32529,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B177" t="n">
         <v>6.351</v>
@@ -32513,7 +32537,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B178" t="n">
         <v>6.277</v>
@@ -32521,7 +32545,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B179" t="n">
         <v>6.49181818181818</v>
@@ -32529,7 +32553,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B180" t="n">
         <v>6.92142857142857</v>
@@ -32537,7 +32561,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B181" t="n">
         <v>6.95285714285714</v>
@@ -32545,7 +32569,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B182" t="n">
         <v>7.22409090909091</v>
@@ -32553,7 +32577,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B183" t="n">
         <v>7.71125</v>
@@ -32561,7 +32585,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B184" t="n">
         <v>8.38380952380952</v>
@@ -32569,7 +32593,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B185" t="n">
         <v>8.32136363636364</v>
@@ -32577,7 +32601,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B186" t="n">
         <v>8.42105263157895</v>
@@ -32585,7 +32609,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B187" t="n">
         <v>8.55809523809524</v>
@@ -37449,7 +37473,7 @@
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>1073</v>
+        <v>881</v>
       </c>
       <c r="B795" t="n">
         <v>2.278</v>
@@ -37460,7 +37484,7 @@
         <v>1074</v>
       </c>
       <c r="B796" t="n">
-        <v>2.26</v>
+        <v>2.31375</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -37484,7 +37484,7 @@
         <v>1074</v>
       </c>
       <c r="B796" t="n">
-        <v>2.31375</v>
+        <v>2.328</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C08 Figures.xlsx
+++ b/Data/C08 Figures.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="1075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="1076">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -2668,6 +2668,9 @@
     <t xml:space="preserve">Aug 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Sep 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">UnempRate</t>
   </si>
   <si>
@@ -3244,7 +3247,7 @@
     <t xml:space="preserve">Jun 1968</t>
   </si>
   <si>
-    <t xml:space="preserve">Sep 2026</t>
+    <t xml:space="preserve">Oct 2026</t>
   </si>
 </sst>
 </file>
@@ -18985,6 +18988,14 @@
         <v>21173.1</v>
       </c>
     </row>
+    <row r="610">
+      <c r="A610" t="s">
+        <v>882</v>
+      </c>
+      <c r="B610" t="n">
+        <v>21104.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -19002,7 +19013,7 @@
         <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="2">
@@ -23867,6 +23878,14 @@
       </c>
       <c r="B609" t="n">
         <v>6.4</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="s">
+        <v>882</v>
+      </c>
+      <c r="B610" t="n">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -23886,7 +23905,7 @@
         <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="2">
@@ -25507,7 +25526,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B204"/>
     </row>
@@ -25528,12 +25547,12 @@
         <v>264</v>
       </c>
       <c r="B1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B2" t="n">
         <v>12.9667760753128</v>
@@ -25541,7 +25560,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B3" t="n">
         <v>15.0136942094219</v>
@@ -25549,7 +25568,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B4" t="n">
         <v>15.7173673795166</v>
@@ -25557,7 +25576,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B5" t="n">
         <v>15.0083394292738</v>
@@ -25565,7 +25584,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B6" t="n">
         <v>14.1631513522075</v>
@@ -25573,7 +25592,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B7" t="n">
         <v>14.3196627658395</v>
@@ -25581,7 +25600,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B8" t="n">
         <v>14.5659126107761</v>
@@ -25589,7 +25608,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B9" t="n">
         <v>11.0934019859703</v>
@@ -25597,7 +25616,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B10" t="n">
         <v>11.5193520347377</v>
@@ -25605,7 +25624,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B11" t="n">
         <v>10.3976063805748</v>
@@ -25613,7 +25632,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B12" t="n">
         <v>10.203544223433</v>
@@ -25621,7 +25640,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B13" t="n">
         <v>8.25370377873824</v>
@@ -25629,7 +25648,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B14" t="n">
         <v>6.74941660698323</v>
@@ -25637,7 +25656,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B15" t="n">
         <v>6.99352943674983</v>
@@ -25645,7 +25664,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B16" t="n">
         <v>8.54641293280502</v>
@@ -25653,7 +25672,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B17" t="n">
         <v>8.36923199167487</v>
@@ -25661,7 +25680,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B18" t="n">
         <v>8.27326635899438</v>
@@ -25669,7 +25688,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B19" t="n">
         <v>9.85826112039194</v>
@@ -25677,7 +25696,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B20" t="n">
         <v>9.91121604952369</v>
@@ -25685,7 +25704,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B21" t="n">
         <v>10.5072207560502</v>
@@ -25693,7 +25712,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B22" t="n">
         <v>7.79066458038734</v>
@@ -25701,7 +25720,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B23" t="n">
         <v>10.9032596283834</v>
@@ -25709,7 +25728,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B24" t="n">
         <v>8.19610135662233</v>
@@ -25717,7 +25736,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B25" t="n">
         <v>9.07734774781358</v>
@@ -25725,7 +25744,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B26" t="n">
         <v>8.50235678691241</v>
@@ -25733,7 +25752,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B27" t="n">
         <v>9.00143117812621</v>
@@ -25741,7 +25760,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B28" t="n">
         <v>9.09344352882898</v>
@@ -25749,7 +25768,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B29" t="n">
         <v>8.12556120408371</v>
@@ -25757,7 +25776,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B30" t="n">
         <v>10.7444231936402</v>
@@ -25765,7 +25784,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B31" t="n">
         <v>10.0971199004294</v>
@@ -25773,7 +25792,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B32" t="n">
         <v>11.4278274718587</v>
@@ -25781,7 +25800,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B33" t="n">
         <v>12.506561942725</v>
@@ -25789,7 +25808,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B34" t="n">
         <v>14.8525484100527</v>
@@ -25797,7 +25816,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B35" t="n">
         <v>13.9647049646935</v>
@@ -25805,7 +25824,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B36" t="n">
         <v>13.8193035567392</v>
@@ -25813,7 +25832,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B37" t="n">
         <v>14.3299854004434</v>
@@ -25821,7 +25840,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B38" t="n">
         <v>15.3018079241173</v>
@@ -25829,7 +25848,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B39" t="n">
         <v>15.0270385091154</v>
@@ -25837,7 +25856,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B40" t="n">
         <v>13.2518711756956</v>
@@ -25845,7 +25864,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B41" t="n">
         <v>13.1332186179338</v>
@@ -25853,7 +25872,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B42" t="n">
         <v>12.6578401751251</v>
@@ -25861,7 +25880,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B43" t="n">
         <v>11.2954913894953</v>
@@ -25869,7 +25888,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B44" t="n">
         <v>12.7456975920676</v>
@@ -25877,7 +25896,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B45" t="n">
         <v>12.0988566109835</v>
@@ -25885,7 +25904,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B46" t="n">
         <v>12.4954011343489</v>
@@ -25893,7 +25912,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B47" t="n">
         <v>14.2289904200083</v>
@@ -25901,7 +25920,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B48" t="n">
         <v>13.4484012949889</v>
@@ -25909,7 +25928,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B49" t="n">
         <v>15.6988273068042</v>
@@ -25917,7 +25936,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B50" t="n">
         <v>14.2845925451855</v>
@@ -25925,7 +25944,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B51" t="n">
         <v>13.7513624713095</v>
@@ -25933,7 +25952,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B52" t="n">
         <v>16.5561760195999</v>
@@ -25941,7 +25960,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B53" t="n">
         <v>15.9924726433944</v>
@@ -25949,7 +25968,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B54" t="n">
         <v>16.8425831874094</v>
@@ -25957,7 +25976,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B55" t="n">
         <v>16.5276746861153</v>
@@ -25965,7 +25984,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B56" t="n">
         <v>16.4698895002538</v>
@@ -25973,7 +25992,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B57" t="n">
         <v>17.2134250823613</v>
@@ -25981,7 +26000,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B58" t="n">
         <v>15.6816081666631</v>
@@ -25989,7 +26008,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B59" t="n">
         <v>14.8028853950233</v>
@@ -25997,7 +26016,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B60" t="n">
         <v>15.2426482221366</v>
@@ -26005,7 +26024,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B61" t="n">
         <v>15.6902851909184</v>
@@ -26013,7 +26032,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B62" t="n">
         <v>16.5013128950056</v>
@@ -26021,7 +26040,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B63" t="n">
         <v>17.144059922985</v>
@@ -26029,7 +26048,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B64" t="n">
         <v>17.3090733250565</v>
@@ -26037,7 +26056,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B65" t="n">
         <v>19.1915260629344</v>
@@ -26045,7 +26064,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B66" t="n">
         <v>22.7683604016704</v>
@@ -26053,7 +26072,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B67" t="n">
         <v>23.3483213053937</v>
@@ -26061,7 +26080,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B68" t="n">
         <v>23.7330017100268</v>
@@ -26069,7 +26088,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B69" t="n">
         <v>24.5746121277929</v>
@@ -26077,7 +26096,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B70" t="n">
         <v>25.299565253288</v>
@@ -26085,7 +26104,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B71" t="n">
         <v>25.0912717707172</v>
@@ -26093,7 +26112,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B72" t="n">
         <v>23.9521568788769</v>
@@ -26101,7 +26120,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B73" t="n">
         <v>21.1869735832747</v>
@@ -26109,7 +26128,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B74" t="n">
         <v>20.6527071997174</v>
@@ -26117,7 +26136,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B75" t="n">
         <v>20.1659943690496</v>
@@ -26125,7 +26144,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B76" t="n">
         <v>18.9358160000968</v>
@@ -26133,7 +26152,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B77" t="n">
         <v>16.9203967093089</v>
@@ -26141,7 +26160,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B78" t="n">
         <v>12.907810848208</v>
@@ -26149,7 +26168,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B79" t="n">
         <v>12.4545658937996</v>
@@ -26157,7 +26176,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B80" t="n">
         <v>13.2184526911685</v>
@@ -26165,7 +26184,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B81" t="n">
         <v>14.2594274489356</v>
@@ -26173,7 +26192,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B82" t="n">
         <v>14.1362614616155</v>
@@ -26181,7 +26200,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B83" t="n">
         <v>17.5108308988957</v>
@@ -26189,7 +26208,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B84" t="n">
         <v>17.8203047316368</v>
@@ -26197,7 +26216,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B85" t="n">
         <v>19.6199365813437</v>
@@ -26205,7 +26224,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B86" t="n">
         <v>18.3178769926645</v>
@@ -26213,7 +26232,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B87" t="n">
         <v>16.4922800191838</v>
@@ -26221,7 +26240,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B88" t="n">
         <v>18.0934981429238</v>
@@ -26229,7 +26248,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B89" t="n">
         <v>14.9717615097796</v>
@@ -26237,7 +26256,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B90" t="n">
         <v>15.137570465284</v>
@@ -26245,7 +26264,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B91" t="n">
         <v>17.0502997395172</v>
@@ -31121,15 +31140,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B2" t="n">
         <v>3.02666666666667</v>
@@ -31137,7 +31156,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B3" t="n">
         <v>2.66</v>
@@ -31145,7 +31164,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B4" t="n">
         <v>1.93285714285714</v>
@@ -31153,7 +31172,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B5" t="n">
         <v>2.59368421052632</v>
@@ -31161,7 +31180,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B6" t="n">
         <v>3.37809523809524</v>
@@ -31169,7 +31188,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B7" t="n">
         <v>3.61809523809524</v>
@@ -31177,7 +31196,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B8" t="n">
         <v>3.19952380952381</v>
@@ -31185,7 +31204,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B9" t="n">
         <v>3.0585</v>
@@ -31193,7 +31212,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B10" t="n">
         <v>3.20818181818182</v>
@@ -31201,7 +31220,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B11" t="n">
         <v>3.27578947368421</v>
@@ -31209,7 +31228,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B12" t="n">
         <v>3.18227272727273</v>
@@ -31217,7 +31236,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B13" t="n">
         <v>2.79714285714286</v>
@@ -31225,7 +31244,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B14" t="n">
         <v>2.6</v>
@@ -31233,7 +31252,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B15" t="n">
         <v>2.4995652173913</v>
@@ -31241,7 +31260,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B16" t="n">
         <v>2.381</v>
@@ -31249,7 +31268,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B17" t="n">
         <v>2.52666666666667</v>
@@ -31257,7 +31276,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B18" t="n">
         <v>2.39909090909091</v>
@@ -31265,7 +31284,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B19" t="n">
         <v>2.73526315789474</v>
@@ -31273,7 +31292,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B20" t="n">
         <v>3.06681818181818</v>
@@ -31281,7 +31300,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B21" t="n">
         <v>3.0855</v>
@@ -31289,7 +31308,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B22" t="n">
         <v>3.10681818181818</v>
@@ -31297,7 +31316,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B23" t="n">
         <v>3.07421052631579</v>
@@ -31305,7 +31324,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B24" t="n">
         <v>3.31772727272727</v>
@@ -31313,7 +31332,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B25" t="n">
         <v>4.24</v>
@@ -31321,7 +31340,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B26" t="n">
         <v>5.3725</v>
@@ -31329,7 +31348,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B27" t="n">
         <v>5.12</v>
@@ -31337,7 +31356,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B28" t="n">
         <v>5.01055555555556</v>
@@ -31345,7 +31364,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B29" t="n">
         <v>4.515</v>
@@ -31353,7 +31372,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B30" t="n">
         <v>3.85909090909091</v>
@@ -31361,7 +31380,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B31" t="n">
         <v>3.835</v>
@@ -31369,7 +31388,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B32" t="n">
         <v>3.83181818181818</v>
@@ -31377,7 +31396,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B33" t="n">
         <v>3.6535</v>
@@ -31385,7 +31404,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B34" t="n">
         <v>3.61904761904762</v>
@@ -31393,7 +31412,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B35" t="n">
         <v>3.5955</v>
@@ -31401,7 +31420,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B36" t="n">
         <v>3.37176470588235</v>
@@ -31409,7 +31428,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B37" t="n">
         <v>3.21842105263158</v>
@@ -31417,7 +31436,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B38" t="n">
         <v>3.37227272727273</v>
@@ -31425,7 +31444,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B39" t="n">
         <v>3.60190476190476</v>
@@ -31433,7 +31452,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B40" t="n">
         <v>3.688</v>
@@ -31441,7 +31460,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B41" t="n">
         <v>3.55136363636364</v>
@@ -31449,7 +31468,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B42" t="n">
         <v>3.622</v>
@@ -31457,7 +31476,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B43" t="n">
         <v>3.6925</v>
@@ -31465,7 +31484,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B44" t="n">
         <v>3.76</v>
@@ -31473,7 +31492,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B45" t="n">
         <v>3.7965</v>
@@ -31481,7 +31500,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B46" t="n">
         <v>3.8715</v>
@@ -31489,7 +31508,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B47" t="n">
         <v>3.74</v>
@@ -31497,7 +31516,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B48" t="n">
         <v>3.655</v>
@@ -31505,7 +31524,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B49" t="n">
         <v>3.54545454545455</v>
@@ -31513,7 +31532,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B50" t="n">
         <v>3.58952380952381</v>
@@ -31521,7 +31540,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B51" t="n">
         <v>3.78380952380952</v>
@@ -31529,7 +31548,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B52" t="n">
         <v>3.79809523809524</v>
@@ -31537,7 +31556,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B53" t="n">
         <v>3.69761904761905</v>
@@ -31545,7 +31564,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B54" t="n">
         <v>3.72315789473684</v>
@@ -31553,7 +31572,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B55" t="n">
         <v>3.84227272727273</v>
@@ -31561,7 +31580,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B56" t="n">
         <v>3.776</v>
@@ -31569,7 +31588,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B57" t="n">
         <v>3.7135</v>
@@ -31577,7 +31596,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B58" t="n">
         <v>3.7004347826087</v>
@@ -31585,7 +31604,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B59" t="n">
         <v>3.655</v>
@@ -31593,7 +31612,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B60" t="n">
         <v>3.8395</v>
@@ -31601,7 +31620,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B61" t="n">
         <v>3.95363636363636</v>
@@ -31609,7 +31628,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B62" t="n">
         <v>3.98190476190476</v>
@@ -31617,7 +31636,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B63" t="n">
         <v>4.08</v>
@@ -31625,7 +31644,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B64" t="n">
         <v>4.10428571428571</v>
@@ -31633,7 +31652,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B65" t="n">
         <v>4.1465</v>
@@ -31641,7 +31660,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B66" t="n">
         <v>4.17619047619048</v>
@@ -31649,7 +31668,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B67" t="n">
         <v>4.44045454545455</v>
@@ -31657,7 +31676,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B68" t="n">
         <v>4.59526315789474</v>
@@ -31665,7 +31684,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B69" t="n">
         <v>4.658</v>
@@ -31673,7 +31692,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B70" t="n">
         <v>4.84</v>
@@ -31681,7 +31700,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B71" t="n">
         <v>5.077</v>
@@ -31689,7 +31708,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B72" t="n">
         <v>5.08952380952381</v>
@@ -31697,7 +31716,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B73" t="n">
         <v>5.05090909090909</v>
@@ -31705,7 +31724,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B74" t="n">
         <v>5.06052631578947</v>
@@ -31713,7 +31732,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B75" t="n">
         <v>5.05</v>
@@ -31721,7 +31740,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B76" t="n">
         <v>5.01571428571429</v>
@@ -31729,7 +31748,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B77" t="n">
         <v>5.113</v>
@@ -31737,7 +31756,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B78" t="n">
         <v>5.19619047619048</v>
@@ -31745,7 +31764,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B79" t="n">
         <v>5.071</v>
@@ -31753,7 +31772,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B80" t="n">
         <v>4.82904761904762</v>
@@ -31761,7 +31780,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B81" t="n">
         <v>4.595</v>
@@ -31769,7 +31788,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B82" t="n">
         <v>4.27045454545455</v>
@@ -31777,7 +31796,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B83" t="n">
         <v>4.0045</v>
@@ -31785,7 +31804,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B84" t="n">
         <v>4.11954545454545</v>
@@ -31793,7 +31812,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B85" t="n">
         <v>4.33722222222222</v>
@@ -31801,7 +31820,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B86" t="n">
         <v>4.273</v>
@@ -31809,7 +31828,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B87" t="n">
         <v>4.32952380952381</v>
@@ -31817,7 +31836,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B88" t="n">
         <v>4.475</v>
@@ -31825,7 +31844,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B89" t="n">
         <v>4.90857142857143</v>
@@ -31833,7 +31852,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B90" t="n">
         <v>5.13904761904762</v>
@@ -31841,7 +31860,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B91" t="n">
         <v>5.753</v>
@@ -31849,7 +31868,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B92" t="n">
         <v>5.99181818181818</v>
@@ -31857,7 +31876,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B93" t="n">
         <v>6.60666666666667</v>
@@ -31865,7 +31884,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B94" t="n">
         <v>6.92285714285714</v>
@@ -31873,7 +31892,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B95" t="n">
         <v>6.91142857142857</v>
@@ -31881,7 +31900,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B96" t="n">
         <v>6.94714285714286</v>
@@ -31889,7 +31908,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B97" t="n">
         <v>6.7675</v>
@@ -31897,7 +31916,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B98" t="n">
         <v>6.23157894736842</v>
@@ -31905,7 +31924,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B99" t="n">
         <v>5.8</v>
@@ -31913,7 +31932,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B100" t="n">
         <v>5.59</v>
@@ -31921,7 +31940,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B101" t="n">
         <v>5.62636363636364</v>
@@ -31929,7 +31948,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B102" t="n">
         <v>5.6305</v>
@@ -31937,7 +31956,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B103" t="n">
         <v>5.898</v>
@@ -31945,7 +31964,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B104" t="n">
         <v>6.38272727272727</v>
@@ -31953,7 +31972,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B105" t="n">
         <v>6.28842105263158</v>
@@ -31961,7 +31980,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B106" t="n">
         <v>6.60571428571429</v>
@@ -31969,7 +31988,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B107" t="n">
         <v>6.67333333333333</v>
@@ -31977,7 +31996,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B108" t="n">
         <v>6.74571428571429</v>
@@ -31985,7 +32004,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B109" t="n">
         <v>6.9905</v>
@@ -31993,7 +32012,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B110" t="n">
         <v>7.44210526315789</v>
@@ -32001,7 +32020,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B111" t="n">
         <v>7.62666666666667</v>
@@ -32009,7 +32028,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B112" t="n">
         <v>7.73761904761905</v>
@@ -32017,7 +32036,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B113" t="n">
         <v>7.68363636363636</v>
@@ -32025,7 +32044,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B114" t="n">
         <v>7.69</v>
@@ -32033,7 +32052,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B115" t="n">
         <v>7.77117647058823</v>
@@ -32041,7 +32060,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B116" t="n">
         <v>7.80666666666667</v>
@@ -32049,7 +32068,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B117" t="n">
         <v>7.718125</v>
@@ -32057,7 +32076,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B118" t="n">
         <v>7.38857142857143</v>
@@ -32065,7 +32084,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B119" t="n">
         <v>6.80947368421053</v>
@@ -32073,7 +32092,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B120" t="n">
         <v>6.57315789473684</v>
@@ -32081,7 +32100,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B121" t="n">
         <v>5.92904761904762</v>
@@ -32089,7 +32108,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B122" t="n">
         <v>5.76611111111111</v>
@@ -32097,7 +32116,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B123" t="n">
         <v>5.676</v>
@@ -32105,7 +32124,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B124" t="n">
         <v>5.46285714285714</v>
@@ -32113,7 +32132,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B125" t="n">
         <v>5.30380952380952</v>
@@ -32121,7 +32140,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B126" t="n">
         <v>4.821875</v>
@@ -32129,7 +32148,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B127" t="n">
         <v>4.46105263157895</v>
@@ -32137,7 +32156,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B128" t="n">
         <v>4.583</v>
@@ -32145,7 +32164,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B129" t="n">
         <v>4.62421052631579</v>
@@ -32153,7 +32172,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B130" t="n">
         <v>3.36818181818182</v>
@@ -32161,7 +32180,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B131" t="n">
         <v>3.07333333333333</v>
@@ -32169,7 +32188,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B132" t="n">
         <v>3.0535</v>
@@ -32177,7 +32196,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B133" t="n">
         <v>3.10954545454545</v>
@@ -32185,7 +32204,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B134" t="n">
         <v>3.54142857142857</v>
@@ -32193,7 +32212,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B135" t="n">
         <v>3.87136363636364</v>
@@ -32201,7 +32220,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B136" t="n">
         <v>3.89666666666667</v>
@@ -32209,7 +32228,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B137" t="n">
         <v>3.848</v>
@@ -32217,7 +32236,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B138" t="n">
         <v>3.33285714285714</v>
@@ -32225,7 +32244,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B139" t="n">
         <v>3.24636363636364</v>
@@ -32233,7 +32252,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B140" t="n">
         <v>3.281</v>
@@ -32241,7 +32260,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B141" t="n">
         <v>3.47789473684211</v>
@@ -32249,7 +32268,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B142" t="n">
         <v>3.4952380952381</v>
@@ -32257,7 +32276,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B143" t="n">
         <v>3.64052631578947</v>
@@ -32265,7 +32284,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B144" t="n">
         <v>3.66952380952381</v>
@@ -32273,7 +32292,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B145" t="n">
         <v>3.61590909090909</v>
@@ -32281,7 +32300,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B146" t="n">
         <v>3.4875</v>
@@ -32289,7 +32308,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B147" t="n">
         <v>3.46</v>
@@ -32297,7 +32316,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B148" t="n">
         <v>3.5605</v>
@@ -32305,7 +32324,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B149" t="n">
         <v>3.56857142857143</v>
@@ -32313,7 +32332,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B150" t="n">
         <v>3.60571428571429</v>
@@ -32321,7 +32340,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B151" t="n">
         <v>3.67736842105263</v>
@@ -32329,7 +32348,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B152" t="n">
         <v>3.77727272727273</v>
@@ -32337,7 +32356,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B153" t="n">
         <v>3.925</v>
@@ -32345,7 +32364,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B154" t="n">
         <v>4.25636363636364</v>
@@ -32353,7 +32372,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B155" t="n">
         <v>4.71444444444444</v>
@@ -32361,7 +32380,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B156" t="n">
         <v>5.10681818181818</v>
@@ -32369,7 +32388,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B157" t="n">
         <v>5.35666666666667</v>
@@ -32377,7 +32396,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B158" t="n">
         <v>5.65285714285714</v>
@@ -32385,7 +32404,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B159" t="n">
         <v>6.01136363636364</v>
@@ -32393,7 +32412,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B160" t="n">
         <v>6.38105263157895</v>
@@ -32401,7 +32420,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B161" t="n">
         <v>6.48545454545455</v>
@@ -32409,7 +32428,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B162" t="n">
         <v>6.45952380952381</v>
@@ -32417,7 +32436,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B163" t="n">
         <v>6.38263157894737</v>
@@ -32425,7 +32444,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B164" t="n">
         <v>6.29090909090909</v>
@@ -32433,7 +32452,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B165" t="n">
         <v>6.1445</v>
@@ -32441,7 +32460,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B166" t="n">
         <v>6.25</v>
@@ -32449,7 +32468,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B167" t="n">
         <v>7.23571428571429</v>
@@ -32457,7 +32476,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B168" t="n">
         <v>8.28</v>
@@ -32465,7 +32484,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B169" t="n">
         <v>8.6555</v>
@@ -32473,7 +32492,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B170" t="n">
         <v>8.87954545454545</v>
@@ -32481,7 +32500,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B171" t="n">
         <v>9.09666666666667</v>
@@ -32489,7 +32508,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B172" t="n">
         <v>9.026</v>
@@ -32497,7 +32516,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B173" t="n">
         <v>8.63681818181818</v>
@@ -32505,7 +32524,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B174" t="n">
         <v>7.827</v>
@@ -32513,7 +32532,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B175" t="n">
         <v>7.3205</v>
@@ -32521,7 +32540,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B176" t="n">
         <v>6.65090909090909</v>
@@ -32529,7 +32548,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B177" t="n">
         <v>6.351</v>
@@ -32537,7 +32556,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B178" t="n">
         <v>6.277</v>
@@ -32545,7 +32564,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B179" t="n">
         <v>6.49181818181818</v>
@@ -32553,7 +32572,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B180" t="n">
         <v>6.92142857142857</v>
@@ -32561,7 +32580,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B181" t="n">
         <v>6.95285714285714</v>
@@ -32569,7 +32588,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B182" t="n">
         <v>7.22409090909091</v>
@@ -32577,7 +32596,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B183" t="n">
         <v>7.71125</v>
@@ -32585,7 +32604,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B184" t="n">
         <v>8.38380952380952</v>
@@ -32593,7 +32612,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B185" t="n">
         <v>8.32136363636364</v>
@@ -32601,7 +32620,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B186" t="n">
         <v>8.42105263157895</v>
@@ -32609,7 +32628,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B187" t="n">
         <v>8.55809523809524</v>
@@ -37481,10 +37500,18 @@
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>1074</v>
+        <v>882</v>
       </c>
       <c r="B796" t="n">
         <v>2.328</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B797" t="n">
+        <v>2.384</v>
       </c>
     </row>
   </sheetData>
